--- a/Result/profitability/3388.xlsx
+++ b/Result/profitability/3388.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>2.17</v>
       </c>
       <c r="M2" t="n">
-        <v>1.2225</v>
+        <v>1.355</v>
       </c>
       <c r="N2" t="n">
-        <v>17.64375</v>
+        <v>18.1125</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -681,7 +681,7 @@
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>2.17</v>
       </c>
       <c r="M3" t="n">
-        <v>1.35</v>
+        <v>1.48875</v>
       </c>
       <c r="N3" t="n">
-        <v>17.625</v>
+        <v>18.18375</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -792,7 +792,7 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -899,25 +899,25 @@
         <v>2.18</v>
       </c>
       <c r="M4" t="n">
-        <v>1.485</v>
+        <v>1.64375</v>
       </c>
       <c r="N4" t="n">
-        <v>17.56</v>
+        <v>17.96625</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
       </c>
       <c r="P4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.78</v>
       </c>
       <c r="M5" t="n">
-        <v>1.27</v>
+        <v>1.4275</v>
       </c>
       <c r="N5" t="n">
-        <v>17.50125</v>
+        <v>17.985</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>1.26875</v>
+        <v>1.3975</v>
       </c>
       <c r="N6" t="n">
-        <v>17.56625</v>
+        <v>17.98625</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>1.86</v>
       </c>
       <c r="M7" t="n">
-        <v>1.35375</v>
+        <v>1.49375</v>
       </c>
       <c r="N7" t="n">
-        <v>17.40375</v>
+        <v>17.79</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>1.6</v>
       </c>
       <c r="M8" t="n">
-        <v>1.4175</v>
+        <v>1.54375</v>
       </c>
       <c r="N8" t="n">
-        <v>17.11375</v>
+        <v>17.29875</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3388</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2381</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1881</v>
+      </c>
+      <c r="E75" t="n">
+        <v>500</v>
+      </c>
+      <c r="F75" t="n">
+        <v>20.99</v>
+      </c>
+      <c r="G75" t="n">
+        <v>233</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>9.80%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>14</v>
+      </c>
+      <c r="J75" t="n">
+        <v>248</v>
+      </c>
+      <c r="K75" t="n">
+        <v>166</v>
+      </c>
+      <c r="L75" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.2275</v>
+      </c>
+      <c r="N75" t="n">
+        <v>18.08125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.8416666666666668</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>1.479999999999997</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.07585853408508436</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>1.326315789473684</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>3.869999999999997</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.2260514018691586</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
